--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486725_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486725_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. PARRONDO CASTRO</t>
+          <t>C. LUIS QUINTERO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0807</v>
+        <v>1.9713</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4157</v>
+        <v>1.6969</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.335</v>
+        <v>0.2743</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4968</v>
+        <v>0.1022</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0133</v>
+        <v>-0.7591</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5101</v>
+        <v>0.8613</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5052</v>
+        <v>2.4212</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1601</v>
+        <v>2.4144</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3451</v>
+        <v>0.0069</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.0084</v>
+        <v>-2.319</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.1733</v>
+        <v>-3.1735</v>
       </c>
       <c r="O2" t="n">
-        <v>0.165</v>
+        <v>0.8544</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.5446</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9308</v>
+        <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0146</v>
+        <v>-0.9032</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7725</v>
+        <v>-0.9866</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2421</v>
+        <v>0.0834</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5985</v>
+        <v>1.2277</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6138</v>
+        <v>1.2277</v>
       </c>
       <c r="X2" t="n">
-        <v>0.9847</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. LUIS QUINTERO</t>
+          <t>J. PARRONDO CASTRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9535</v>
+        <v>1.6337</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3315</v>
+        <v>2.4157</v>
       </c>
       <c r="F3" t="n">
-        <v>0.622</v>
+        <v>-0.782</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1022</v>
+        <v>1.4968</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7591</v>
+        <v>-0.0133</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8613</v>
+        <v>1.5101</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4212</v>
+        <v>4.5052</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4144</v>
+        <v>3.1601</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0069</v>
+        <v>1.3451</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.319</v>
+        <v>-3.0084</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.1735</v>
+        <v>-3.1733</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8544</v>
+        <v>0.165</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5446</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R3" t="n">
-        <v>2.51</v>
+        <v>1.9308</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.921</v>
+        <v>-1.4616</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.352</v>
+        <v>-0.7725</v>
       </c>
       <c r="U3" t="n">
-        <v>0.431</v>
+        <v>-0.6891</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2277</v>
+        <v>1.5985</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2277</v>
+        <v>0.6138</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.9847</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.648</v>
+        <v>0.4329</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7023</v>
+        <v>0.2886</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0544</v>
+        <v>0.1443</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1463</v>
@@ -766,13 +766,13 @@
         <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>0.022</v>
+        <v>-0.1931</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3859</v>
+        <v>-0.0278</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.364</v>
+        <v>-0.1653</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0926</v>
+        <v>0.0067</v>
       </c>
       <c r="E5" t="n">
         <v>0.6139</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7064</v>
+        <v>-0.6071</v>
       </c>
       <c r="G5" t="n">
         <v>0.3101</v>
@@ -844,13 +844,13 @@
         <v>0.1931</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5957</v>
+        <v>-0.4964</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4854</v>
+        <v>-0.386</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4282</v>
+        <v>-0.3041</v>
       </c>
       <c r="E6" t="n">
         <v>-0.7451</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3169</v>
+        <v>0.441</v>
       </c>
       <c r="G6" t="n">
         <v>0.1786</v>
@@ -922,13 +922,13 @@
         <v>0.5792</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2207</v>
+        <v>-0.0965</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1655</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0551</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4699</v>
+        <v>-0.4451</v>
       </c>
       <c r="E7" t="n">
         <v>0.1028</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5727</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3664</v>
@@ -1000,13 +1000,13 @@
         <v>0.5792</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3971</v>
+        <v>-0.3723</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3971</v>
+        <v>-0.3723</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2856</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2068</v>
+        <v>-0.7516</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0129</v>
+        <v>-0.806</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1939</v>
+        <v>0.0544</v>
       </c>
       <c r="G8" t="n">
         <v>-0.124</v>
@@ -1078,13 +1078,13 @@
         <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8551</v>
+        <v>-0.4</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5243</v>
+        <v>-0.3174</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3309</v>
+        <v>-0.0825</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6138</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.519</v>
+        <v>-1.526</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5454</v>
+        <v>-2.1799</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0264</v>
+        <v>0.6539</v>
       </c>
       <c r="G9" t="n">
         <v>-3.046</v>
@@ -1156,13 +1156,13 @@
         <v>2.51</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3033</v>
+        <v>-0.3103</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1313</v>
+        <v>-0.7658</v>
       </c>
       <c r="U9" t="n">
-        <v>0.828</v>
+        <v>0.4555</v>
       </c>
       <c r="V9" t="n">
         <v>0.2856</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. GONZALEZ-MONJE PEREZ</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8784</v>
+        <v>-2.6072</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2347</v>
+        <v>-0.1449</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-2.4623</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0561</v>
+        <v>-0.9381</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6341</v>
+        <v>-0.6691</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5779</v>
+        <v>-0.269</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7516</v>
+        <v>0.0207</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0819</v>
+        <v>0.0207</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8334</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8077</v>
+        <v>-0.9588</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5522</v>
+        <v>-0.6898</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2555</v>
+        <v>-0.269</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7377</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8495</v>
+        <v>-0.4413</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9099</v>
+        <v>-0.1655</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0603</v>
+        <v>-0.2758</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5133</v>
+        <v>-1.2277</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5133</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>M. GONZALEZ-MONJE PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6623</v>
+        <v>-2.721</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2</v>
+        <v>-1.9035</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4623</v>
+        <v>-0.8175</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9381</v>
+        <v>-0.0561</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6691</v>
+        <v>-1.6341</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.269</v>
+        <v>1.5779</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0207</v>
+        <v>0.7516</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0207</v>
+        <v>-1.0819</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.8334</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9588</v>
+        <v>-0.8077</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6898</v>
+        <v>-0.5522</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.269</v>
+        <v>-0.2555</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.7377</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4965</v>
+        <v>0.0069</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2207</v>
+        <v>0.2411</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2758</v>
+        <v>-0.2342</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2277</v>
+        <v>-1.5133</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2277</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5708</v>
+        <v>-4.1694</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.818</v>
+        <v>-2.7146</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7528</v>
+        <v>-1.4548</v>
       </c>
       <c r="G12" t="n">
         <v>1.2257</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6494</v>
+        <v>-1.248</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6622</v>
+        <v>-0.5588</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9872</v>
+        <v>-0.6892</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9821</v>
+        <v>-4.3725</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6056</v>
+        <v>-3.3436</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3765</v>
+        <v>-1.0289</v>
       </c>
       <c r="G13" t="n">
         <v>-2.8103</v>
@@ -1468,13 +1468,13 @@
         <v>2.3169</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1405</v>
+        <v>-1.5308</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0485</v>
+        <v>-0.7864</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.092</v>
+        <v>-0.7444</v>
       </c>
       <c r="V13" t="n">
         <v>1.5133</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.1279</v>
+        <v>-12.8523</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.995499999999999</v>
+        <v>-6.7197</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.1323</v>
+        <v>-6.1326</v>
       </c>
       <c r="G14" t="n">
         <v>-4.1738</v>
@@ -1546,10 +1546,10 @@
         <v>15.4461</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.7224</v>
+        <v>-7.4466</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.6916</v>
+        <v>-4.4156</v>
       </c>
       <c r="U14" t="n">
         <v>-3.0309</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3208</v>
+        <v>4.8133</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2237</v>
+        <v>2.6032</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0971</v>
+        <v>2.2102</v>
       </c>
       <c r="G15" t="n">
         <v>3.9554</v>
@@ -1624,13 +1624,13 @@
         <v>1.1585</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5005</v>
+        <v>0.9931</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0479</v>
+        <v>0.4273</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4527</v>
+        <v>0.5657</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3282</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8489</v>
+        <v>3.9494</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8885</v>
+        <v>2.1987</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9605</v>
+        <v>1.7507</v>
       </c>
       <c r="G16" t="n">
         <v>3.0706</v>
@@ -1702,13 +1702,13 @@
         <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>0.265</v>
+        <v>0.3655</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.745</v>
+        <v>-0.4348</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>0.8003</v>
       </c>
       <c r="V16" t="n">
         <v>0.8995</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>A. NAVAS CERVERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2089</v>
+        <v>3.7002</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4623</v>
+        <v>1.1842</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2534</v>
+        <v>2.516</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1091</v>
+        <v>0.6518</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9659</v>
+        <v>1.0067</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8568</v>
+        <v>-0.3549</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7375</v>
+        <v>1.1013</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6562</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0814</v>
+        <v>0.5766</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6285</v>
+        <v>-0.4495</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6903</v>
+        <v>0.4819</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9382</v>
+        <v>-0.9314</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1931</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1585</v>
+        <v>2.3169</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5632</v>
+        <v>1.1723</v>
       </c>
       <c r="T17" t="n">
-        <v>3.061</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5022</v>
+        <v>0.6486</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6565</v>
+        <v>2.4554</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3709</v>
+        <v>2.4554</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. NAVAS CERVERA</t>
+          <t>I. ESTEBAN GLADER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1734</v>
+        <v>2.3781</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7705</v>
+        <v>0.3923</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4029</v>
+        <v>1.9859</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6518</v>
+        <v>0.9025</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0067</v>
+        <v>0.586</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3549</v>
+        <v>0.3165</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1013</v>
+        <v>0.1442</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.1035</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5766</v>
+        <v>0.0407</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4495</v>
+        <v>0.7583</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4819</v>
+        <v>0.4826</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9314</v>
+        <v>0.2758</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5792</v>
+        <v>1.1585</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3169</v>
+        <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6455</v>
+        <v>0.3172</v>
       </c>
       <c r="T18" t="n">
-        <v>0.11</v>
+        <v>0.2481</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5355</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. ESTEBAN GLADER</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8403</v>
+        <v>1.2936</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0214</v>
+        <v>1.4973</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8617</v>
+        <v>-0.2037</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9025</v>
+        <v>0.1091</v>
       </c>
       <c r="H19" t="n">
-        <v>0.586</v>
+        <v>0.9659</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3165</v>
+        <v>-0.8568</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1442</v>
+        <v>1.7375</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1035</v>
+        <v>1.6562</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0407</v>
+        <v>0.0814</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7583</v>
+        <v>-1.6285</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4826</v>
+        <v>-0.6903</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2758</v>
+        <v>-0.9382</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
         <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2207</v>
+        <v>1.6479</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1655</v>
+        <v>1.096</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0551</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3709</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ROSALES DARIAS</t>
+          <t>E. AMANDIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2245</v>
+        <v>1.1741</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5469</v>
+        <v>2.7616</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3224</v>
+        <v>-1.5875</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2122</v>
+        <v>2.8776</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2205</v>
+        <v>5.4141</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0083</v>
+        <v>-2.5364</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4921</v>
+        <v>5.5272</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1854</v>
+        <v>6.8632</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6775</v>
+        <v>-1.336</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7043</v>
+        <v>-2.6495</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0351</v>
+        <v>-1.4491</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6692</v>
+        <v>-1.2005</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9654</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9308</v>
+        <v>1.3515</v>
       </c>
       <c r="S20" t="n">
-        <v>1.699</v>
+        <v>1.0688</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0202</v>
+        <v>0.1306</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6788</v>
+        <v>0.9382</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2277</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. AMANDIO</t>
+          <t>A. ROSALES DARIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1203</v>
+        <v>1.0218</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6582</v>
+        <v>1.4435</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5379</v>
+        <v>-0.4217</v>
       </c>
       <c r="G21" t="n">
-        <v>2.8776</v>
+        <v>-0.2122</v>
       </c>
       <c r="H21" t="n">
-        <v>5.4141</v>
+        <v>-1.2205</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.5364</v>
+        <v>1.0083</v>
       </c>
       <c r="J21" t="n">
-        <v>5.5272</v>
+        <v>1.4921</v>
       </c>
       <c r="K21" t="n">
-        <v>6.8632</v>
+        <v>-0.1854</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.336</v>
+        <v>1.6775</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6495</v>
+        <v>-1.7043</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4491</v>
+        <v>-1.0351</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2005</v>
+        <v>-0.6692</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3515</v>
+        <v>1.9308</v>
       </c>
       <c r="S21" t="n">
-        <v>1.015</v>
+        <v>1.4963</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0272</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9878</v>
+        <v>0.5795</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4698</v>
+        <v>-0.1388</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2756</v>
+        <v>0.4825</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7454</v>
+        <v>-0.6213</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2971</v>
@@ -2170,13 +2170,13 @@
         <v>1.1585</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3312</v>
+        <v>-0.0001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4139</v>
+        <v>-0.2071</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0828</v>
+        <v>0.2069</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. LUIS HERRERA</t>
+          <t>M. SOSA FRANCO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8252</v>
+        <v>-0.5734</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2897</v>
+        <v>-3.0251</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5355</v>
+        <v>2.4516</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7448</v>
+        <v>-0.9084</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4758</v>
+        <v>0.2829</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.269</v>
+        <v>-1.1913</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6481</v>
+        <v>-1.3286</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6481</v>
+        <v>0.0074</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.336</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0967</v>
+        <v>0.4201</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8277</v>
+        <v>0.2755</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.269</v>
+        <v>0.1447</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1585</v>
+        <v>2.1239</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3749</v>
+        <v>0.4275</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3584</v>
+        <v>0.2343</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0166</v>
+        <v>0.1933</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6138</v>
+        <v>-0.2856</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6138</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. SOSA FRANCO</t>
+          <t>N. LUIS HERRERA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2822</v>
+        <v>-1.0073</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6456</v>
+        <v>-0.4966</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3634</v>
+        <v>-0.5107</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9084</v>
+        <v>-1.7448</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2829</v>
+        <v>-1.4758</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1913</v>
+        <v>-0.269</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3286</v>
+        <v>-0.6481</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0074</v>
+        <v>-0.6481</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.336</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4201</v>
+        <v>-1.0967</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2755</v>
+        <v>-0.8277</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1447</v>
+        <v>-0.269</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1239</v>
+        <v>1.1585</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2813</v>
+        <v>0.1929</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3863</v>
+        <v>0.1515</v>
       </c>
       <c r="U24" t="n">
-        <v>0.105</v>
+        <v>0.0414</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2856</v>
+        <v>-0.6138</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2856</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0319</v>
+        <v>-2.7935</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7365</v>
+        <v>-2.9092</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2954</v>
+        <v>0.1156</v>
       </c>
       <c r="G25" t="n">
         <v>-3.2307</v>
@@ -2404,13 +2404,13 @@
         <v>2.3169</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5076000000000001</v>
+        <v>0.7308</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.883</v>
+        <v>-0.0557</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3754</v>
+        <v>0.7865</v>
       </c>
       <c r="V25" t="n">
         <v>0.2856</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>13.128</v>
+        <v>13.8175</v>
       </c>
       <c r="E26" t="n">
-        <v>6.132499999999999</v>
+        <v>6.132399999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>6.995599999999999</v>
+        <v>7.685099999999999</v>
       </c>
       <c r="G26" t="n">
         <v>4.1738</v>
@@ -2482,13 +2482,13 @@
         <v>17.3771</v>
       </c>
       <c r="S26" t="n">
-        <v>7.722299999999999</v>
+        <v>8.412199999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>3.031</v>
+        <v>3.0307</v>
       </c>
       <c r="U26" t="n">
-        <v>4.691700000000001</v>
+        <v>5.3813</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6989999999999998</v>
